--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_25950_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_25950_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R46d406de2e154699"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R28c6f50c8e8748a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,3096 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>21:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>20:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>13:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>12:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>05:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>04:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>03:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>02:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>01:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>22:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>
